--- a/events/Augsburg_2017_WC/Augsburg_2017_WC_start.xlsx
+++ b/events/Augsburg_2017_WC/Augsburg_2017_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W650"/>
+  <dimension ref="A1:AC650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1317,12 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -1355,12 +1385,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -1423,12 +1453,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -1491,12 +1521,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -1559,12 +1589,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -1627,12 +1657,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -1695,12 +1725,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -1763,12 +1793,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -1831,12 +1861,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -1899,12 +1929,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -1967,12 +1997,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -2035,12 +2065,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -2103,12 +2133,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -2171,12 +2201,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -2239,12 +2269,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -2355,7 +2385,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -2413,7 +2443,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -2471,7 +2501,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -2529,7 +2559,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -2587,7 +2617,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -2645,7 +2675,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -2703,7 +2733,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -2761,7 +2791,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -2819,7 +2849,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -2877,7 +2907,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -2935,7 +2965,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -3046,7 +3076,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -3104,7 +3134,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -3162,7 +3192,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -3220,7 +3250,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -3331,7 +3361,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -3389,7 +3419,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -3447,7 +3477,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -3505,7 +3535,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -3563,7 +3593,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -3674,7 +3704,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -3732,7 +3762,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -3790,7 +3820,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -3848,7 +3878,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3906,7 +3936,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -3964,7 +3994,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -4022,7 +4052,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -4133,7 +4163,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -4191,7 +4221,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -4249,7 +4279,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -4307,7 +4337,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -4365,7 +4395,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -4423,7 +4453,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -4481,7 +4511,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -4539,7 +4569,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -4597,7 +4627,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -4655,7 +4685,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -4713,7 +4743,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -4771,7 +4801,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -4829,7 +4859,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -4887,7 +4917,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -4945,7 +4975,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -5003,7 +5033,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -5061,7 +5091,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -5119,7 +5149,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -5177,7 +5207,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -5235,7 +5265,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -5293,7 +5323,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -5351,7 +5381,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -5409,7 +5439,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -5467,7 +5497,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -5525,7 +5555,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -5583,7 +5613,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -5641,7 +5671,7 @@
           <t>TEUNISSEN Marnix</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35695</t>
         </is>
@@ -5699,7 +5729,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -5757,7 +5787,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -5815,7 +5845,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -5873,7 +5903,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -5931,7 +5961,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -5989,7 +6019,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -6047,7 +6077,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -6105,7 +6135,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -6163,7 +6193,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -6221,7 +6251,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -6279,7 +6309,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -6337,7 +6367,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -6395,7 +6425,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -6453,7 +6483,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -6511,7 +6541,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -6569,7 +6599,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -6627,7 +6657,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -6685,7 +6715,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -6743,7 +6773,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -6801,7 +6831,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -6859,7 +6889,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -6917,7 +6947,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -7028,7 +7058,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -7086,7 +7116,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -7144,7 +7174,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -7202,7 +7232,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -7260,7 +7290,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -7318,7 +7348,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -7376,7 +7406,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -7434,7 +7464,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -7492,7 +7522,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -7550,7 +7580,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -7608,7 +7638,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -7666,7 +7696,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -7777,7 +7807,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -7835,7 +7865,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -7893,7 +7923,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -7951,7 +7981,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -8009,7 +8039,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -8067,7 +8097,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -8125,7 +8155,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -8183,7 +8213,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8241,7 +8271,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -8299,7 +8329,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -8357,7 +8387,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -8415,7 +8445,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -8473,7 +8503,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -8531,7 +8561,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -8589,7 +8619,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -8647,7 +8677,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -8705,7 +8735,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -8763,7 +8793,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -8821,7 +8851,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -8879,7 +8909,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -8937,7 +8967,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -8995,7 +9025,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -9053,7 +9083,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -9111,7 +9141,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -9169,7 +9199,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -9227,7 +9257,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -9285,7 +9315,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -9343,7 +9373,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -9401,7 +9431,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -9464,12 +9494,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr">
+      <c r="Y155" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -9580,7 +9610,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -9638,7 +9668,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -9696,7 +9726,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -9754,7 +9784,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -9812,7 +9842,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -9870,7 +9900,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -9928,7 +9958,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -9986,7 +10016,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -10097,7 +10127,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -10155,7 +10185,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -10213,7 +10243,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -10324,7 +10354,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -10382,7 +10412,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -10440,7 +10470,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -10498,7 +10528,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -10609,7 +10639,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10667,7 +10697,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -10725,7 +10755,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -10783,7 +10813,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -10841,7 +10871,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -10899,7 +10929,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -10957,7 +10987,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -11015,7 +11045,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -11073,7 +11103,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -11131,7 +11161,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -11189,7 +11219,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -11247,7 +11277,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -11305,7 +11335,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -11363,7 +11393,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -11421,7 +11451,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -11479,7 +11509,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -11537,7 +11567,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -11595,7 +11625,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -11653,7 +11683,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -11711,7 +11741,7 @@
           <t>TEUNISSEN Marnix</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35695</t>
         </is>
@@ -11769,7 +11799,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -11827,7 +11857,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -11885,7 +11915,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -11943,7 +11973,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -12001,7 +12031,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -12059,7 +12089,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -12117,7 +12147,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -12175,7 +12205,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -12233,7 +12263,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -12291,7 +12321,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -12349,7 +12379,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -12407,7 +12437,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -12465,7 +12495,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -12523,7 +12553,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -12581,7 +12611,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -12639,7 +12669,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -12697,7 +12727,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -12808,7 +12838,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -12866,7 +12896,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -12924,7 +12954,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -12982,7 +13012,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -13040,7 +13070,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -13098,7 +13128,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -13156,7 +13186,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -13214,7 +13244,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -13325,7 +13355,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -13383,7 +13413,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -13441,7 +13471,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -13499,7 +13529,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -13557,7 +13587,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -13615,7 +13645,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -13673,7 +13703,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -13731,7 +13761,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -13789,7 +13819,7 @@
           <t>POLAT Gamze</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>71755</t>
         </is>
@@ -13847,7 +13877,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -13905,7 +13935,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -13963,7 +13993,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -14021,7 +14051,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -14079,7 +14109,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -14137,7 +14167,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -14195,7 +14225,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -14253,7 +14283,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -14311,7 +14341,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -14369,7 +14399,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -14427,7 +14457,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -14485,7 +14515,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -14543,7 +14573,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -14654,7 +14684,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -14712,7 +14742,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -14823,7 +14853,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -14881,7 +14911,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -14939,7 +14969,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -14997,7 +15027,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -15055,7 +15085,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -15113,7 +15143,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -15171,7 +15201,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -15229,7 +15259,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -15287,7 +15317,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -15345,7 +15375,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -15403,7 +15433,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -15461,7 +15491,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -15519,7 +15549,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -15577,7 +15607,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -15635,7 +15665,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -15693,7 +15723,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -15751,7 +15781,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -15809,7 +15839,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -15867,7 +15897,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -15925,7 +15955,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -15983,7 +16013,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -16041,7 +16071,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -16099,7 +16129,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -16157,7 +16187,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -16215,7 +16245,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -16273,7 +16303,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -16331,7 +16361,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -16389,7 +16419,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -16447,7 +16477,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -16505,7 +16535,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -16563,7 +16593,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -16621,7 +16651,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -16679,7 +16709,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -16737,7 +16767,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -16795,7 +16825,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -16853,7 +16883,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -16911,7 +16941,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -16969,7 +16999,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -17027,7 +17057,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -17085,7 +17115,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -17143,7 +17173,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -17201,7 +17231,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -17259,7 +17289,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -17317,7 +17347,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -17375,7 +17405,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -17433,7 +17463,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -17491,7 +17521,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -17549,7 +17579,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -17607,7 +17637,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -17665,7 +17695,7 @@
           <t>CIFTCI Murat</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>43512</t>
         </is>
@@ -17723,7 +17753,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -17781,7 +17811,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -17839,7 +17869,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -17897,7 +17927,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -17955,7 +17985,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -18013,7 +18043,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -18071,7 +18101,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -18129,7 +18159,7 @@
           <t>JORDAN Frantisek</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35057</t>
         </is>
@@ -18187,7 +18217,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -18245,7 +18275,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -18303,7 +18333,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -18361,7 +18391,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -18419,7 +18449,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -18477,7 +18507,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -18535,7 +18565,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -18593,7 +18623,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -18651,7 +18681,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -18709,7 +18739,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -18767,7 +18797,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -18825,7 +18855,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -18883,7 +18913,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -18941,7 +18971,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -18999,7 +19029,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -19057,7 +19087,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -19115,7 +19145,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -19173,7 +19203,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -19231,7 +19261,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -19289,7 +19319,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -19347,7 +19377,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -19405,7 +19435,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -19463,7 +19493,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -19521,7 +19551,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -19579,7 +19609,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -19637,7 +19667,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -19695,7 +19725,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -19806,7 +19836,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -19864,7 +19894,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -19922,7 +19952,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -19980,7 +20010,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -20038,7 +20068,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -20096,7 +20126,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -20154,7 +20184,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -20212,7 +20242,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -20270,7 +20300,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -20328,7 +20358,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -20386,7 +20416,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -20444,7 +20474,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -20502,7 +20532,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -20560,7 +20590,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -20618,7 +20648,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -20676,7 +20706,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -20734,7 +20764,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -20792,7 +20822,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -20850,7 +20880,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -20908,7 +20938,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -20966,7 +20996,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -21024,7 +21054,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -21082,7 +21112,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -21140,7 +21170,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -21198,7 +21228,7 @@
           <t>POLAT Gamze</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>71755</t>
         </is>
@@ -21256,7 +21286,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -21314,7 +21344,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -21372,7 +21402,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -21430,7 +21460,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -21488,7 +21518,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -21546,7 +21576,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -21604,7 +21634,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -21662,7 +21692,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -21720,7 +21750,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -21778,7 +21808,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -21836,7 +21866,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -21894,7 +21924,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -21952,7 +21982,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -22063,7 +22093,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -22121,7 +22151,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -22232,7 +22262,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -22290,7 +22320,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -22348,7 +22378,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -22406,7 +22436,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -22464,7 +22494,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -22522,7 +22552,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -22580,7 +22610,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -22638,7 +22668,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -22696,7 +22726,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -22754,7 +22784,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -22812,7 +22842,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -22870,7 +22900,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -22928,7 +22958,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -22986,7 +23016,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -23044,7 +23074,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -23102,7 +23132,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -23160,7 +23190,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -23218,7 +23248,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -23276,7 +23306,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -23334,7 +23364,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -23392,7 +23422,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -23450,7 +23480,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -23508,7 +23538,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -23566,7 +23596,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -23624,7 +23654,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -23682,7 +23712,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -23740,7 +23770,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -23798,7 +23828,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -23856,7 +23886,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -23914,7 +23944,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -23972,7 +24002,7 @@
           <t>CIFTCI Murat</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>43512</t>
         </is>
@@ -24030,7 +24060,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -24088,7 +24118,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -24146,7 +24176,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -24204,7 +24234,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -24262,7 +24292,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -24320,7 +24350,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -24378,7 +24408,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -24436,7 +24466,7 @@
           <t>JORDAN Frantisek</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35057</t>
         </is>
@@ -24494,7 +24524,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -24552,7 +24582,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -24610,7 +24640,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -24668,7 +24698,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -24726,7 +24756,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -24784,7 +24814,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -24842,7 +24872,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -24900,7 +24930,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -24958,7 +24988,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -25016,7 +25046,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -25074,7 +25104,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -25132,7 +25162,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -25190,7 +25220,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -25248,7 +25278,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -25306,7 +25336,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -25364,7 +25394,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -25422,7 +25452,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -25480,7 +25510,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -25538,7 +25568,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -25596,7 +25626,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -25654,7 +25684,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -25712,7 +25742,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -25770,7 +25800,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -25828,7 +25858,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -25939,7 +25969,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -25997,7 +26027,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -26055,7 +26085,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -26113,7 +26143,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -26171,7 +26201,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -26229,7 +26259,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -26287,7 +26317,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -26345,7 +26375,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -26673,12 +26703,12 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -26741,12 +26771,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V454" t="inlineStr">
+      <c r="Y454" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -26809,12 +26839,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -26877,12 +26907,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V456" t="inlineStr">
+      <c r="Y456" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -26945,12 +26975,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -27013,12 +27043,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -27081,12 +27111,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -27149,12 +27179,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -27217,12 +27247,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V461" t="inlineStr">
+      <c r="Y461" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -27285,12 +27315,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V462" t="inlineStr">
+      <c r="Y462" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -27353,12 +27383,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V463" t="inlineStr">
+      <c r="Y463" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -27421,12 +27451,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V464" t="inlineStr">
+      <c r="Y464" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -27489,12 +27519,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V465" t="inlineStr">
+      <c r="Y465" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -27557,12 +27587,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -27620,7 +27650,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -27678,7 +27708,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -27736,7 +27766,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -27794,7 +27824,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -27852,7 +27882,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -27910,7 +27940,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -27968,7 +27998,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -28026,7 +28056,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -28084,7 +28114,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -28142,7 +28172,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -28200,7 +28230,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -28258,7 +28288,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -28316,7 +28346,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -28374,7 +28404,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -28432,7 +28462,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -28490,7 +28520,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -28548,7 +28578,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -28606,7 +28636,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -28664,7 +28694,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -28722,7 +28752,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -28780,7 +28810,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -28891,7 +28921,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -28949,7 +28979,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -29007,7 +29037,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -29065,7 +29095,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -29123,7 +29153,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -29181,7 +29211,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -29239,7 +29269,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -29297,7 +29327,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -29355,7 +29385,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -29413,7 +29443,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -29471,7 +29501,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -29529,7 +29559,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -29587,7 +29617,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -29645,7 +29675,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -29703,7 +29733,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -29761,7 +29791,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29819,7 +29849,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -29877,7 +29907,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -29935,7 +29965,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -29993,7 +30023,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -30051,7 +30081,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -30109,7 +30139,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -30167,7 +30197,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -30225,7 +30255,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -30283,7 +30313,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -30341,7 +30371,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -30399,7 +30429,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -30457,7 +30487,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -30515,7 +30545,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -30573,7 +30603,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -30631,7 +30661,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -30689,7 +30719,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -30747,7 +30777,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -30805,7 +30835,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -30863,7 +30893,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -30921,7 +30951,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -30979,7 +31009,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -31037,7 +31067,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -31095,7 +31125,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -31153,7 +31183,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -31211,7 +31241,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -31269,7 +31299,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -31327,7 +31357,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -31385,7 +31415,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -31443,7 +31473,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -31501,7 +31531,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -31559,7 +31589,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -31617,7 +31647,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -31690,12 +31720,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V537" t="inlineStr">
+      <c r="Y537" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -31768,12 +31798,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V538" t="inlineStr">
+      <c r="Y538" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -31846,12 +31876,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V539" t="inlineStr">
+      <c r="Y539" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -31924,12 +31954,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V540" t="inlineStr">
+      <c r="Y540" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -32002,12 +32032,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V541" t="inlineStr">
+      <c r="Y541" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -32080,12 +32110,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V542" t="inlineStr">
+      <c r="Y542" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -32158,12 +32188,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V543" t="inlineStr">
+      <c r="Y543" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -32236,12 +32266,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V544" t="inlineStr">
+      <c r="Y544" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -32314,12 +32344,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V545" t="inlineStr">
+      <c r="Y545" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -32392,12 +32422,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V546" t="inlineStr">
+      <c r="Y546" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -32465,7 +32495,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -32533,7 +32563,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -32601,7 +32631,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -32669,7 +32699,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -32737,7 +32767,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -32805,7 +32835,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -32936,7 +32966,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -33004,7 +33034,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -33072,7 +33102,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -33140,7 +33170,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -33208,7 +33238,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -33276,7 +33306,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -33344,7 +33374,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -33412,7 +33442,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -33480,7 +33510,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -33548,7 +33578,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -33616,7 +33646,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -33684,7 +33714,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -33752,7 +33782,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -34022,7 +34052,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -34080,7 +34110,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -34138,7 +34168,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -34196,7 +34226,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -34254,7 +34284,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -34312,7 +34342,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -34370,7 +34400,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -34428,7 +34458,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -34486,7 +34516,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -34544,7 +34574,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -34602,7 +34632,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -34660,7 +34690,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -34718,7 +34748,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -34776,7 +34806,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -34834,7 +34864,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -34892,7 +34922,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -34950,7 +34980,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -35008,7 +35038,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -35066,7 +35096,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -35124,7 +35154,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -35182,7 +35212,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -35240,7 +35270,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -35298,7 +35328,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -35356,7 +35386,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -35414,7 +35444,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -35472,7 +35502,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -35530,7 +35560,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -35588,7 +35618,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -35646,7 +35676,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -35704,7 +35734,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -35762,7 +35792,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -35820,7 +35850,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -35878,7 +35908,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -35936,7 +35966,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -35994,7 +36024,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -36052,7 +36082,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -36110,7 +36140,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -36168,7 +36198,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -36226,7 +36256,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -36284,7 +36314,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -36342,7 +36372,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -36400,7 +36430,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -36458,7 +36488,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -36516,7 +36546,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -36574,7 +36604,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -36632,7 +36662,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -36690,7 +36720,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -36748,7 +36778,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -36806,7 +36836,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -36864,7 +36894,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -36922,7 +36952,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -36980,7 +37010,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -37038,7 +37068,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -37096,7 +37126,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -37154,7 +37184,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -37212,7 +37242,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -37270,7 +37300,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -37328,7 +37358,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -37386,7 +37416,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -37444,7 +37474,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -37512,7 +37542,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -37580,7 +37610,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -37648,7 +37678,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -37716,7 +37746,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -37784,7 +37814,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -37852,7 +37882,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -37920,7 +37950,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -37988,7 +38018,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -38056,7 +38086,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -38124,7 +38154,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -38192,7 +38222,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -38260,7 +38290,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -38328,7 +38358,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -38396,7 +38426,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -38464,7 +38494,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -38532,7 +38562,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -38600,7 +38630,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -38668,7 +38698,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -38736,7 +38766,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -38804,7 +38834,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
